--- a/90518_REPORT_BOTTEGA_04-01-2026.xlsx
+++ b/90518_REPORT_BOTTEGA_04-01-2026.xlsx
@@ -9,12 +9,13 @@
     <sheet name="VENDUTO FASCIA ORARIA" r:id="rId3" sheetId="1"/>
     <sheet name="ANALISI ARTICOLI" r:id="rId4" sheetId="2"/>
     <sheet name="PDT VENUTI FS GIORNALIERO" r:id="rId5" sheetId="3"/>
+    <sheet name="INGRESSI" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="74">
   <si>
     <t>FASCIA ORARIA</t>
   </si>
@@ -49,6 +50,39 @@
     <t>15:00 - 15:59</t>
   </si>
   <si>
+    <t>16:00 - 16:59</t>
+  </si>
+  <si>
+    <t>17:00 - 17:59</t>
+  </si>
+  <si>
+    <t>18:00 - 18:59</t>
+  </si>
+  <si>
+    <t>19:00 - 19:59</t>
+  </si>
+  <si>
+    <t>20:00 - 20:59</t>
+  </si>
+  <si>
+    <t>21:00 - 21:59</t>
+  </si>
+  <si>
+    <t>22:00 - 22:59</t>
+  </si>
+  <si>
+    <t>23:00 - 23:59</t>
+  </si>
+  <si>
+    <t>0:00 - 0:59</t>
+  </si>
+  <si>
+    <t>1:00 - 1:59</t>
+  </si>
+  <si>
+    <t>2:00 - 2:59</t>
+  </si>
+  <si>
     <t>TOTALE INCASSI 04/01/2026</t>
   </si>
   <si>
@@ -85,22 +119,28 @@
     <t>Tagliata di pollo</t>
   </si>
   <si>
+    <t>50-004-010-000040</t>
+  </si>
+  <si>
+    <t>Mezzo pollo</t>
+  </si>
+  <si>
+    <t>50-004-010-000100</t>
+  </si>
+  <si>
+    <t>Cosce di pollo</t>
+  </si>
+  <si>
     <t>50-004-010-000010</t>
   </si>
   <si>
     <t>Gran piatto per 2</t>
   </si>
   <si>
-    <t>50-004-010-000100</t>
-  </si>
-  <si>
-    <t>Cosce di pollo</t>
-  </si>
-  <si>
-    <t>50-004-010-000040</t>
-  </si>
-  <si>
-    <t>Mezzo pollo</t>
+    <t>50-004-010-000220</t>
+  </si>
+  <si>
+    <t>Riso</t>
   </si>
   <si>
     <t>50-004-010-000160</t>
@@ -109,12 +149,6 @@
     <t>Patate</t>
   </si>
   <si>
-    <t>50-004-010-000220</t>
-  </si>
-  <si>
-    <t>Riso</t>
-  </si>
-  <si>
     <t>50-004-010-000320</t>
   </si>
   <si>
@@ -139,6 +173,12 @@
     <t>Pollo alla cacciatora + contorno</t>
   </si>
   <si>
+    <t>50-004-010-000740</t>
+  </si>
+  <si>
+    <t>Verdure</t>
+  </si>
+  <si>
     <t>50-004-010-000140</t>
   </si>
   <si>
@@ -151,6 +191,24 @@
     <t>Insalata mista</t>
   </si>
   <si>
+    <t>50-004-010-000750</t>
+  </si>
+  <si>
+    <t>Aggiunta Contorno</t>
+  </si>
+  <si>
+    <t>50-004-010-888889</t>
+  </si>
+  <si>
+    <t>Shopper carta</t>
+  </si>
+  <si>
+    <t>50-004-010-888888</t>
+  </si>
+  <si>
+    <t>Shopper BIO</t>
+  </si>
+  <si>
     <t>TOTALE GRUPPO</t>
   </si>
   <si>
@@ -164,6 +222,21 @@
   </si>
   <si>
     <t>12:00-15:59</t>
+  </si>
+  <si>
+    <t>16:00-18:59</t>
+  </si>
+  <si>
+    <t>19:00-02:59</t>
+  </si>
+  <si>
+    <t>04/01/2026</t>
+  </si>
+  <si>
+    <t>VAR %</t>
+  </si>
+  <si>
+    <t>05/01/2025</t>
   </si>
 </sst>
 </file>
@@ -301,7 +374,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true"/>
@@ -314,13 +387,27 @@
     <xf numFmtId="4" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="true" applyBorder="true" applyNumberFormat="true">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="40.59375" customWidth="true" bestFit="true"/>
@@ -404,31 +491,119 @@
         <v>10</v>
       </c>
       <c r="B10" t="n" s="7">
-        <v>144.4547</v>
+        <v>119.1819</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="s" s="1">
+      <c r="A11" t="s" s="2">
         <v>11</v>
       </c>
-      <c r="B11" t="n" s="1">
-        <v>1206.02</v>
+      <c r="B11" t="n" s="5">
+        <v>32.4728</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="s" s="1">
+      <c r="A12" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="B12" t="n" s="1">
-        <v>984.38</v>
+      <c r="B12" t="n" s="7">
+        <v>70.282</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="s" s="1">
+      <c r="A13" t="s" s="2">
         <v>13</v>
       </c>
-      <c r="B13" t="n" s="1">
-        <v>22.52</v>
+      <c r="B13" t="n" s="5">
+        <v>105.629</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="4">
+        <v>14</v>
+      </c>
+      <c r="B14" t="n" s="7">
+        <v>116.6185</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>15</v>
+      </c>
+      <c r="B15" t="n" s="5">
+        <v>230.7637</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n" s="7">
+        <v>23.4545</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>17</v>
+      </c>
+      <c r="B17" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>18</v>
+      </c>
+      <c r="B18" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>19</v>
+      </c>
+      <c r="B19" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="4">
+        <v>20</v>
+      </c>
+      <c r="B20" t="n" s="7">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B21" t="n" s="5">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="1">
+        <v>22</v>
+      </c>
+      <c r="B22" t="n" s="1">
+        <v>1771.69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="1">
+        <v>23</v>
+      </c>
+      <c r="B23" t="n" s="1">
+        <v>1760.28</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="1">
+        <v>24</v>
+      </c>
+      <c r="B24" t="n" s="1">
+        <v>0.65</v>
       </c>
     </row>
   </sheetData>
@@ -438,7 +613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -450,197 +625,197 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>18</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="4">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s" s="4">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n" s="7">
-        <v>621.5454</v>
+        <v>924.109</v>
       </c>
       <c r="D2" t="n" s="7">
-        <v>53.0</v>
+        <v>79.0</v>
       </c>
       <c r="E2" t="n" s="7">
-        <v>51.54</v>
+        <v>52.16</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n" s="5">
-        <v>129.0</v>
+        <v>232.2001</v>
       </c>
       <c r="D3" t="n" s="5">
-        <v>11.0</v>
+        <v>20.0</v>
       </c>
       <c r="E3" t="n" s="5">
-        <v>10.7</v>
+        <v>13.11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C4" t="n" s="7">
-        <v>104.091</v>
+        <v>115.2</v>
       </c>
       <c r="D4" t="n" s="7">
-        <v>5.0</v>
+        <v>13.0</v>
       </c>
       <c r="E4" t="n" s="7">
-        <v>8.63</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
-        <v>88.2</v>
+        <v>104.4</v>
       </c>
       <c r="D5" t="n" s="5">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E5" t="n" s="5">
-        <v>7.31</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C6" t="n" s="7">
-        <v>81.0</v>
+        <v>104.091</v>
       </c>
       <c r="D6" t="n" s="7">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="E6" t="n" s="7">
-        <v>6.72</v>
+        <v>5.88</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="C7" t="n" s="5">
-        <v>53.6365</v>
+        <v>76.3636</v>
       </c>
       <c r="D7" t="n" s="5">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="E7" t="n" s="5">
-        <v>4.45</v>
+        <v>4.31</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="4">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n" s="7">
-        <v>43.6363</v>
+        <v>61.8183</v>
       </c>
       <c r="D8" t="n" s="7">
-        <v>8.0</v>
+        <v>14.0</v>
       </c>
       <c r="E8" t="n" s="7">
-        <v>3.62</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n" s="5">
-        <v>27.0</v>
+        <v>54.0</v>
       </c>
       <c r="D9" t="n" s="5">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="E9" t="n" s="5">
-        <v>2.24</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="4">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="4">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C10" t="n" s="7">
-        <v>23.4546</v>
+        <v>35.1819</v>
       </c>
       <c r="D10" t="n" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="E10" t="n" s="7">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>14.5455</v>
+        <v>26.1819</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E11" t="n" s="5">
-        <v>1.21</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>11.7273</v>
@@ -649,55 +824,123 @@
         <v>1.0</v>
       </c>
       <c r="E12" t="n" s="7">
-        <v>0.97</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>4.5455</v>
+        <v>9.8181</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="E13" t="n" s="5">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="C14" t="n" s="7">
+        <v>9.091</v>
+      </c>
+      <c r="D14" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="E14" t="n" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="C15" t="n" s="5">
         <v>3.6364</v>
       </c>
-      <c r="D14" t="n" s="7">
+      <c r="D15" t="n" s="5">
         <v>1.0</v>
       </c>
-      <c r="E14" t="n" s="7">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s" s="1">
-        <v>45</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" t="n" s="1">
-        <v>1206.02</v>
-      </c>
-      <c r="D15" t="n" s="1">
-        <v>117.0</v>
-      </c>
-      <c r="E15" t="n" s="1">
+      <c r="E15" t="n" s="5">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="B16" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="C16" t="n" s="7">
+        <v>2.7273</v>
+      </c>
+      <c r="D16" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="E16" t="n" s="7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>60</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="C17" t="n" s="5">
+        <v>0.8197</v>
+      </c>
+      <c r="D17" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="E17" t="n" s="5">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B18" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C18" t="n" s="7">
+        <v>0.3279</v>
+      </c>
+      <c r="D18" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="E18" t="n" s="7">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="1">
+        <v>64</v>
+      </c>
+      <c r="B19" s="2"/>
+      <c r="C19" t="n" s="1">
+        <v>1771.69</v>
+      </c>
+      <c r="D19" t="n" s="1">
+        <v>183.0</v>
+      </c>
+      <c r="E19" t="n" s="1">
         <v>100.0</v>
       </c>
     </row>
@@ -708,7 +951,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.359375" customWidth="true" bestFit="true"/>
@@ -719,13 +962,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D1" t="s" s="1">
         <v>1</v>
@@ -733,15 +976,15 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="1">
-        <v>46</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n" s="5">
         <v>6.0</v>
@@ -752,10 +995,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="4">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B4" t="s" s="4">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n" s="7">
         <v>1.0</v>
@@ -766,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C5" t="n" s="5">
         <v>1.0</v>
@@ -780,10 +1023,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="4">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s" s="4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C6" t="n" s="7">
         <v>1.0</v>
@@ -794,10 +1037,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n" s="5">
         <v>1.0</v>
@@ -808,10 +1051,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="1">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="B8" t="s" s="4">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n" s="1">
         <v>10.0</v>
@@ -823,29 +1066,29 @@
     <row r="9"/>
     <row r="10">
       <c r="A10" t="s" s="1">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n" s="5">
-        <v>47.0</v>
+        <v>46.0</v>
       </c>
       <c r="D11" t="n" s="5">
-        <v>551.1818</v>
+        <v>539.4545</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="4">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s" s="4">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n" s="7">
         <v>11.0</v>
@@ -856,24 +1099,24 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n" s="5">
-        <v>11.0</v>
+        <v>10.0</v>
       </c>
       <c r="D13" t="n" s="5">
-        <v>50.0001</v>
+        <v>45.4546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="4">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s" s="4">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C14" t="n" s="7">
         <v>9.0</v>
@@ -884,24 +1127,24 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C15" t="n" s="5">
-        <v>9.0</v>
+        <v>8.0</v>
       </c>
       <c r="D15" t="n" s="5">
-        <v>81.0</v>
+        <v>72.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="4">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s" s="4">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C16" t="n" s="7">
         <v>7.0</v>
@@ -912,10 +1155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="C17" t="n" s="5">
         <v>4.0</v>
@@ -926,10 +1169,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="4">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s" s="4">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C18" t="n" s="7">
         <v>3.0</v>
@@ -940,10 +1183,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C19" t="n" s="5">
         <v>2.0</v>
@@ -954,10 +1197,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="4">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s" s="4">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="C20" t="n" s="7">
         <v>1.0</v>
@@ -968,10 +1211,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="C21" t="n" s="5">
         <v>1.0</v>
@@ -982,10 +1225,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="4">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="B22" t="s" s="4">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C22" t="n" s="7">
         <v>1.0</v>
@@ -996,10 +1239,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C23" t="n" s="5">
         <v>1.0</v>
@@ -1010,26 +1253,388 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="B24" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C24" t="n" s="1">
+        <v>104.0</v>
+      </c>
+      <c r="D24" t="n" s="1">
+        <v>1073.27</v>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" t="s" s="1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>35</v>
+      </c>
+      <c r="C27" t="n" s="5">
+        <v>4.0</v>
+      </c>
+      <c r="D27" t="n" s="5">
+        <v>34.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="4">
+        <v>40</v>
+      </c>
+      <c r="B28" t="s" s="4">
+        <v>41</v>
+      </c>
+      <c r="C28" t="n" s="7">
+        <v>4.0</v>
+      </c>
+      <c r="D28" t="n" s="7">
+        <v>21.8182</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="C29" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D29" t="n" s="5">
+        <v>35.1819</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="4">
+        <v>30</v>
+      </c>
+      <c r="B30" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C30" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D30" t="n" s="7">
+        <v>35.1818</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>45</v>
+      </c>
+      <c r="C31" t="n" s="5">
+        <v>3.0</v>
+      </c>
+      <c r="D31" t="n" s="5">
+        <v>27.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="4">
+        <v>58</v>
+      </c>
+      <c r="B32" t="s" s="4">
+        <v>59</v>
+      </c>
+      <c r="C32" t="n" s="7">
+        <v>3.0</v>
+      </c>
+      <c r="D32" t="n" s="7">
+        <v>2.7273</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>37</v>
+      </c>
+      <c r="C33" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D33" t="n" s="5">
+        <v>16.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="4">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s" s="4">
+        <v>53</v>
+      </c>
+      <c r="C34" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D34" t="n" s="7">
+        <v>9.8181</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C35" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D35" t="n" s="5">
+        <v>9.0909</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="4">
+        <v>60</v>
+      </c>
+      <c r="B36" t="s" s="4">
+        <v>61</v>
+      </c>
+      <c r="C36" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D36" t="n" s="7">
+        <v>0.8197</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="C37" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D37" t="n" s="5">
+        <v>0.164</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="B38" t="s" s="4">
+        <v>49</v>
+      </c>
+      <c r="C38" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D38" t="n" s="7">
+        <v>11.6364</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>54</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="C39" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D39" t="n" s="5">
+        <v>4.5455</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C40" t="n" s="1">
+        <v>32.0</v>
+      </c>
+      <c r="D40" t="n" s="1">
+        <v>208.38</v>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" t="s" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>31</v>
+      </c>
+      <c r="C43" t="n" s="5">
+        <v>24.0</v>
+      </c>
+      <c r="D43" t="n" s="5">
+        <v>279.1091</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s" s="4">
+        <v>32</v>
+      </c>
+      <c r="B44" t="s" s="4">
+        <v>33</v>
+      </c>
+      <c r="C44" t="n" s="7">
+        <v>6.0</v>
+      </c>
+      <c r="D44" t="n" s="7">
+        <v>68.0182</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="C45" t="n" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="D45" t="n" s="5">
+        <v>10.9091</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="4">
+        <v>62</v>
+      </c>
+      <c r="B46" t="s" s="4">
+        <v>63</v>
+      </c>
+      <c r="C46" t="n" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="D46" t="n" s="7">
+        <v>0.1639</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="B24" t="s" s="4">
-        <v>48</v>
-      </c>
-      <c r="C24" t="n" s="1">
-        <v>107.0</v>
-      </c>
-      <c r="D24" t="n" s="1">
-        <v>1098.55</v>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="C47" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D47" t="n" s="5">
+        <v>11.7273</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s" s="4">
+        <v>36</v>
+      </c>
+      <c r="B48" t="s" s="4">
+        <v>37</v>
+      </c>
+      <c r="C48" t="n" s="7">
+        <v>1.0</v>
+      </c>
+      <c r="D48" t="n" s="7">
+        <v>9.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>43</v>
+      </c>
+      <c r="C49" t="n" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="D49" t="n" s="5">
+        <v>3.6364</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s" s="1">
+        <v>66</v>
+      </c>
+      <c r="B50" t="s" s="4">
+        <v>67</v>
+      </c>
+      <c r="C50" t="n" s="1">
+        <v>37.0</v>
+      </c>
+      <c r="D50" t="n" s="1">
+        <v>382.56</v>
+      </c>
+    </row>
+    <row r="51"/>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A8:B8"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A50:B50"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="12.73046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="7.9140625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.73046875" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>71</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>72</v>
+      </c>
+      <c r="C1" t="s" s="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n" s="9">
+        <v>7250.0</v>
+      </c>
+      <c r="B2" s="12" t="n">
+        <f>(A2-C2)/C2</f>
+        <v>0.0</v>
+      </c>
+      <c r="C2" t="n" s="9">
+        <v>8008.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>